--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487855_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487855_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9695</v>
+        <v>5.0307</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5484</v>
+        <v>3.7564</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4211</v>
+        <v>1.2743</v>
       </c>
       <c r="G2" t="n">
         <v>1.5019</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1138</v>
+        <v>1.175</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5031</v>
+        <v>0.7111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6107</v>
+        <v>0.4639</v>
       </c>
       <c r="V2" t="n">
         <v>1.5213</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9677</v>
+        <v>3.1255</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4184</v>
+        <v>3.8111</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4507</v>
+        <v>-0.6856</v>
       </c>
       <c r="G3" t="n">
         <v>0.675</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9495</v>
+        <v>1.1073</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4256</v>
+        <v>0.8182</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5239</v>
+        <v>0.2891</v>
       </c>
       <c r="V3" t="n">
         <v>0.9268999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7248</v>
+        <v>2.5541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5048</v>
+        <v>1.0406</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2199</v>
+        <v>1.5135</v>
       </c>
       <c r="G4" t="n">
         <v>0.7000999999999999</v>
@@ -766,13 +766,13 @@
         <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.351</v>
+        <v>0.4784</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4567</v>
+        <v>0.0791</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1057</v>
+        <v>0.3993</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2642</v>
+        <v>1.0308</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2973</v>
+        <v>1.6084</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5615</v>
+        <v>-0.5776</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8465</v>
+        <v>-3.1624</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4456</v>
+        <v>-1.9982</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4009</v>
+        <v>-1.1642</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6629</v>
+        <v>-2.4314</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8377</v>
+        <v>-0.4058</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1747</v>
+        <v>-2.0256</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1835</v>
+        <v>-0.731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3921</v>
+        <v>-1.5924</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5756</v>
+        <v>0.8613</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1218</v>
+        <v>-0.2081</v>
       </c>
       <c r="R5" t="n">
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9695</v>
+        <v>0.7261</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9316</v>
+        <v>0.5153</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0379</v>
+        <v>0.2108</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1132</v>
+        <v>2.2183</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>3.7325</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1168</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8454</v>
+        <v>0.9525</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8246</v>
+        <v>-0.7174</v>
       </c>
       <c r="F6" t="n">
         <v>1.67</v>
@@ -922,10 +922,10 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0776</v>
+        <v>0.0295</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.4024</v>
       </c>
       <c r="U6" t="n">
         <v>0.4319</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5075</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1145</v>
+        <v>-0.7259</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.607</v>
+        <v>1.4734</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1624</v>
+        <v>1.8465</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9982</v>
+        <v>1.4456</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1642</v>
+        <v>0.4009</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4314</v>
+        <v>1.6629</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4058</v>
+        <v>1.8377</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0256</v>
+        <v>-0.1747</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.731</v>
+        <v>0.1835</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5924</v>
+        <v>-0.3921</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8613</v>
+        <v>0.5756</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2487</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2081</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2029</v>
+        <v>0.4528</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0215</v>
+        <v>0.503</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1814</v>
+        <v>-0.0502</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2183</v>
+        <v>0.1132</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7325</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5142</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9882</v>
+        <v>-1.5112</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.196</v>
+        <v>-1.6603</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2078</v>
+        <v>0.1491</v>
       </c>
       <c r="G8" t="n">
         <v>-2.033</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1416</v>
+        <v>0.3355</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1305</v>
+        <v>0.4053</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0111</v>
+        <v>-0.0698</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5428</v>
+        <v>-1.9367</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3177</v>
+        <v>-0.1676</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2251</v>
+        <v>-1.7691</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-2.3592</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5607</v>
+        <v>-0.2642</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8989</v>
+        <v>-2.0949</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5588</v>
+        <v>0.9353</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6952</v>
+        <v>1.324</v>
       </c>
       <c r="L9" t="n">
-        <v>1.254</v>
+        <v>-0.3886</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2207</v>
+        <v>-3.2945</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8655</v>
+        <v>-1.5882</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3551</v>
+        <v>-1.7063</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4974</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6165</v>
+        <v>0.4224</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4534</v>
+        <v>0.1458</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1631</v>
+        <v>0.2767</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6449</v>
+        <v>-2.334</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8758</v>
+        <v>-1.0991</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7691</v>
+        <v>-1.2349</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3592</v>
+        <v>-2.7134</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2642</v>
+        <v>-0.0788</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0949</v>
+        <v>-2.6346</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9353</v>
+        <v>-0.411</v>
       </c>
       <c r="K10" t="n">
-        <v>1.324</v>
+        <v>0.9786</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3886</v>
+        <v>-1.3896</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2945</v>
+        <v>-2.3025</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5882</v>
+        <v>-1.0574</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7063</v>
+        <v>-1.245</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2857</v>
+        <v>0.65</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5624</v>
+        <v>0.3524</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2767</v>
+        <v>0.2975</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7841</v>
+        <v>-2.6103</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7812</v>
+        <v>-2.532</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.003</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9711</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1067</v>
+        <v>-1.5607</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1355</v>
+        <v>0.8989</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1356</v>
+        <v>0.5588</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9918</v>
+        <v>-0.6952</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1275</v>
+        <v>1.254</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1068</v>
+        <v>-1.2207</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1148</v>
+        <v>-0.8655</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9919</v>
+        <v>-0.3551</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4162</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0812</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0124</v>
+        <v>0.549</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1643</v>
+        <v>0.2391</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.152</v>
+        <v>0.3099</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5908</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9644</v>
+        <v>-2.7189</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7001</v>
+        <v>-1.7159</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2643</v>
+        <v>-1.003</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7134</v>
+        <v>-2.9711</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0788</v>
+        <v>-3.1067</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6346</v>
+        <v>0.1355</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.411</v>
+        <v>0.1356</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9786</v>
+        <v>-0.9918</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3896</v>
+        <v>1.1275</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3025</v>
+        <v>-3.1068</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0574</v>
+        <v>-2.1148</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.245</v>
+        <v>-0.9919</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0196</v>
+        <v>0.0776</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2486</v>
+        <v>0.2296</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2682</v>
+        <v>-0.152</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3538</v>
+        <v>0.5908</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3538</v>
+        <v>0.5908</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3422</v>
+        <v>-2.9914</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4833</v>
+        <v>-2.1618</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.859</v>
+        <v>-0.8296</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2313</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1109</v>
+        <v>0.2399</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3791</v>
+        <v>-0.0576</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2682</v>
+        <v>0.2975</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9874999999999994</v>
+        <v>-0.6614000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8899000000000008</v>
+        <v>-0.5635000000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09789999999999965</v>
+        <v>-0.0978</v>
       </c>
       <c r="G14" t="n">
         <v>-12.4095</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.612500000000001</v>
+        <v>-2.6125</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.796900000000001</v>
+        <v>-9.796899999999999</v>
       </c>
       <c r="J14" t="n">
         <v>2.0838</v>
@@ -1546,22 +1546,22 @@
         <v>12.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>5.9174</v>
+        <v>6.243500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2126</v>
+        <v>3.5389</v>
       </c>
       <c r="U14" t="n">
         <v>2.7046</v>
       </c>
       <c r="V14" t="n">
-        <v>6.545</v>
+        <v>6.544999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>7.3412</v>
+        <v>7.341200000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7961999999999999</v>
+        <v>-0.7962</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9842</v>
+        <v>5.0788</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6623</v>
+        <v>4.4124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3219</v>
+        <v>0.6664</v>
       </c>
       <c r="G15" t="n">
         <v>4.0445</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2872</v>
+        <v>-0.1926</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7581</v>
+        <v>-0.008</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5291</v>
+        <v>-0.1846</v>
       </c>
       <c r="V15" t="n">
         <v>-0.23</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5526</v>
+        <v>2.8466</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1955</v>
+        <v>1.8393</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3571</v>
+        <v>1.0074</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5515</v>
+        <v>2.4068</v>
       </c>
       <c r="H16" t="n">
-        <v>1.966</v>
+        <v>0.627</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5855</v>
+        <v>1.7798</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5966</v>
+        <v>2.4355</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2642</v>
+        <v>0.7292</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3324</v>
+        <v>1.7063</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0451</v>
+        <v>-0.0287</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2982</v>
+        <v>-0.1022</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2531</v>
+        <v>0.0735</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2695</v>
+        <v>-0.4551</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4501</v>
+        <v>-0.2424</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7196</v>
+        <v>-0.2127</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9376</v>
+        <v>-0.3538</v>
       </c>
       <c r="W16" t="n">
-        <v>0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4562</v>
+        <v>2.2683</v>
       </c>
       <c r="E17" t="n">
-        <v>1.625</v>
+        <v>1.4454</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8312</v>
+        <v>0.8229</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4068</v>
+        <v>3.5515</v>
       </c>
       <c r="H17" t="n">
-        <v>0.627</v>
+        <v>1.966</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7798</v>
+        <v>1.5855</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4355</v>
+        <v>3.5966</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7292</v>
+        <v>2.2642</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7063</v>
+        <v>1.3324</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0287</v>
+        <v>-0.0451</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1022</v>
+        <v>-0.2982</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0735</v>
+        <v>0.2531</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8455</v>
+        <v>-0.5537</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4567</v>
+        <v>-0.3</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3888</v>
+        <v>-0.2537</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3538</v>
+        <v>-0.9376</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3538</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8635</v>
+        <v>1.6824</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7483</v>
+        <v>2.1053</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8848</v>
+        <v>-0.4229</v>
       </c>
       <c r="G18" t="n">
         <v>1.8206</v>
@@ -1858,13 +1858,13 @@
         <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4404</v>
+        <v>0.2593</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9968</v>
+        <v>0.3539</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5565</v>
+        <v>-0.0946</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8137</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8651</v>
+        <v>1.0921</v>
       </c>
       <c r="E19" t="n">
         <v>0.8575</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0076</v>
+        <v>0.2347</v>
       </c>
       <c r="G19" t="n">
         <v>2.4009</v>
@@ -1936,13 +1936,13 @@
         <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8064</v>
+        <v>-0.5793</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2395</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5669</v>
+        <v>-0.3398</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9376</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1562</v>
+        <v>0.8016</v>
       </c>
       <c r="E20" t="n">
-        <v>0.19</v>
+        <v>0.7258</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0337</v>
+        <v>0.0759</v>
       </c>
       <c r="G20" t="n">
         <v>1.3603</v>
@@ -2014,13 +2014,13 @@
         <v>1.8731</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.869</v>
+        <v>-0.2236</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3667</v>
+        <v>0.1691</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5023</v>
+        <v>-0.3927</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1675</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8756</v>
+        <v>-1.947</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6697</v>
+        <v>-1.7644</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2059</v>
+        <v>-0.1827</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.138</v>
+        <v>-0.4888</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0043</v>
+        <v>-2.1812</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8662</v>
+        <v>1.6924</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1847</v>
+        <v>-0.5906</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1063</v>
+        <v>-0.7808</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0784</v>
+        <v>0.1902</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3227</v>
+        <v>0.1018</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1106</v>
+        <v>-1.4005</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7879</v>
+        <v>1.5022</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2218</v>
+        <v>-0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.46</v>
+        <v>-0.4662</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6818</v>
+        <v>0.2806</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7513</v>
+        <v>-2.1051</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3538</v>
+        <v>-0.7076</v>
       </c>
       <c r="X22" t="n">
         <v>-1.3975</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3669</v>
+        <v>-2.4065</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.55</v>
+        <v>-1.9912</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8168</v>
+        <v>-0.4153</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4888</v>
+        <v>-0.138</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1812</v>
+        <v>-1.0043</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6924</v>
+        <v>0.8662</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5906</v>
+        <v>0.1847</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7808</v>
+        <v>0.1063</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1902</v>
+        <v>0.0784</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1018</v>
+        <v>-0.3227</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4005</v>
+        <v>-1.1106</v>
       </c>
       <c r="O23" t="n">
-        <v>1.5022</v>
+        <v>0.7879</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R23" t="n">
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6054</v>
+        <v>-0.3091</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2519</v>
+        <v>-0.7815</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3536</v>
+        <v>0.4724</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1051</v>
+        <v>-1.7513</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7076</v>
+        <v>-0.3538</v>
       </c>
       <c r="X23" t="n">
         <v>-1.3975</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9459</v>
+        <v>-2.71</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9517</v>
+        <v>-3.7374</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0059</v>
+        <v>1.0274</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4272</v>
@@ -2326,13 +2326,13 @@
         <v>0.4162</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5238</v>
+        <v>-0.288</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1286</v>
+        <v>0.1501</v>
       </c>
       <c r="V24" t="n">
         <v>1.7513</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1697</v>
+        <v>-3.0435</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9178</v>
+        <v>-3.7035</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7481</v>
+        <v>0.66</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8623</v>
@@ -2404,13 +2404,13 @@
         <v>1.8731</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0993</v>
+        <v>-0.9731</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8358</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2635</v>
+        <v>-0.3516</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9875000000000012</v>
+        <v>3.1306</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09810000000000185</v>
+        <v>0.09789999999999921</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8897</v>
+        <v>3.0329</v>
       </c>
       <c r="G26" t="n">
         <v>12.4095</v>
@@ -2470,7 +2470,7 @@
         <v>-8.003399999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>5.9191</v>
+        <v>5.919099999999999</v>
       </c>
       <c r="P26" t="n">
         <v>1.0406</v>
@@ -2482,16 +2482,16 @@
         <v>13.5277</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.917299999999999</v>
+        <v>-3.7742</v>
       </c>
       <c r="T26" t="n">
         <v>-2.7047</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2128</v>
+        <v>-1.0695</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.545299999999999</v>
+        <v>-6.545300000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0.7961</v>
